--- a/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD92232-3E81-4CE2-96D7-2B7F4E009087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAECD8C-4055-45AC-B98D-87F02F5D432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,10 +69,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -89,18 +85,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>vulnerable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Attack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>weak</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,10 +97,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Skill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Poison</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,10 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Artifact</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>IsDebuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,6 +158,21 @@
   </si>
   <si>
     <t>免疫下一次 Debuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Immune</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -185,7 +180,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +201,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -717,14 +718,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -735,231 +736,214 @@
         <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
+      <c r="D4" s="1">
+        <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F4" s="1">
-        <v>99</v>
-      </c>
-      <c r="G4" s="1">
         <v>2</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
+      <c r="D5" s="1">
+        <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F5" s="1">
-        <v>99</v>
-      </c>
-      <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>32</v>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
+      <c r="D6" s="1">
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1">
-        <v>99</v>
-      </c>
-      <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>33</v>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
+      <c r="D7" s="1">
+        <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F7" s="1">
-        <v>99</v>
-      </c>
-      <c r="G7" s="1">
         <v>-1</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>34</v>
+      <c r="G7" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
+      <c r="D8" s="1">
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F8" s="1">
-        <v>99</v>
-      </c>
-      <c r="G8" s="1">
         <v>-1</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>35</v>
+      <c r="G8" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>16</v>
+      <c r="D9" s="1">
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1">
-        <v>99</v>
-      </c>
-      <c r="G9" s="1">
         <v>-1</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="G9" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAECD8C-4055-45AC-B98D-87F02F5D432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B86094-C03F-4922-B1B2-95A3CB5BCCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -118,14 +118,6 @@
   </si>
   <si>
     <t>叠层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Duration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -718,14 +710,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -742,13 +734,10 @@
         <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -765,13 +754,10 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -788,13 +774,10 @@
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -810,14 +793,11 @@
       <c r="E4" s="1">
         <v>99</v>
       </c>
-      <c r="F4" s="1">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -833,14 +813,11 @@
       <c r="E5" s="1">
         <v>99</v>
       </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>27</v>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -856,14 +833,11 @@
       <c r="E6" s="1">
         <v>99</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
+      <c r="F6" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -879,14 +853,11 @@
       <c r="E7" s="1">
         <v>99</v>
       </c>
-      <c r="F7" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
+      <c r="F7" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -902,19 +873,16 @@
       <c r="E8" s="1">
         <v>99</v>
       </c>
-      <c r="F8" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>30</v>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -925,21 +893,17 @@
       <c r="E9" s="1">
         <v>99</v>
       </c>
-      <c r="F9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>31</v>
+      <c r="F9" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAECD8C-4055-45AC-B98D-87F02F5D432A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F6EEE1-31D9-4365-BB81-8C15751688A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,18 +117,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>叠层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Duration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -142,10 +130,6 @@
   </si>
   <si>
     <t>造成伤害减少 {0}%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成伤害 +{0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -173,6 +157,22 @@
       </rPr>
       <t> </t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大叠层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害 +{0}%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -739,13 +739,13 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -785,13 +785,13 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -808,13 +808,13 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
         <v>99</v>
       </c>
-      <c r="F4" s="1">
-        <v>2</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -831,13 +831,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1">
         <v>99</v>
       </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -854,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
         <v>99</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
         <v>99</v>
       </c>
-      <c r="F7" s="1">
-        <v>-1</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -900,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
         <v>99</v>
       </c>
-      <c r="F8" s="1">
-        <v>-1</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
@@ -914,7 +914,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
         <v>99</v>
       </c>
-      <c r="F9" s="1">
-        <v>-1</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F6EEE1-31D9-4365-BB81-8C15751688A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B168D80-B867-4DE4-A137-4D553FD40908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -121,10 +121,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DefaultDuration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>受到伤害增加 {0}%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -173,6 +169,10 @@
   </si>
   <si>
     <t>造成伤害 +{0}%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -718,14 +718,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -739,16 +739,17 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -770,8 +771,9 @@
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -785,16 +787,17 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -814,10 +817,11 @@
         <v>99</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -837,10 +841,11 @@
         <v>99</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -860,10 +865,11 @@
         <v>99</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -883,10 +889,11 @@
         <v>99</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -906,15 +913,16 @@
         <v>99</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -929,10 +937,11 @@
         <v>99</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -940,6 +949,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B168D80-B867-4DE4-A137-4D553FD40908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D51B1B-22A0-434C-866D-B0CDA16F9231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuffConfig" sheetId="1" r:id="rId1"/>
@@ -85,14 +85,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>vulnerable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weak</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Strength</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -174,6 +166,13 @@
   <si>
     <t>Description</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vulnerable_power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weak_power</t>
   </si>
 </sst>
 </file>
@@ -736,16 +735,16 @@
         <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="H1" s="1"/>
     </row>
@@ -784,16 +783,16 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="H3" s="1"/>
     </row>
@@ -802,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
@@ -817,7 +816,7 @@
         <v>99</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -826,7 +825,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -841,7 +840,7 @@
         <v>99</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1"/>
     </row>
@@ -850,7 +849,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -865,7 +864,7 @@
         <v>99</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -874,7 +873,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -889,7 +888,7 @@
         <v>99</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -898,7 +897,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -913,7 +912,7 @@
         <v>99</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H8" s="1"/>
     </row>
@@ -922,7 +921,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -937,7 +936,7 @@
         <v>99</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H9" s="1"/>
     </row>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D51B1B-22A0-434C-866D-B0CDA16F9231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD404C78-AD07-4B96-B76F-555CC304BF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,18 +45,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中毒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>再生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>免疫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -85,18 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Strength</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Poison</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Regeneration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>IsDebuff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,33 +97,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每回合受到 {0} 点伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每回合恢复 {0} 点生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>免疫下一次 Debuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Immune</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>最大叠层</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,10 +109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>造成伤害 +{0}%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -173,13 +118,32 @@
   </si>
   <si>
     <t>weak_power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害 +{0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击伤害减少{0}%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strength_power</t>
+  </si>
+  <si>
+    <t>shrink_power</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +154,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -200,12 +165,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -717,91 +676,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
@@ -810,22 +766,21 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F4" s="1">
         <v>99</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1"/>
+        <v>14</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -834,22 +789,21 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1">
         <v>99</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="1"/>
+        <v>15</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -858,97 +812,37 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>99</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1"/>
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1">
         <v>99</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
-        <v>5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>99</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>99</v>
-      </c>
-      <c r="G9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/BuffConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD404C78-AD07-4B96-B76F-555CC304BF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6BC699-5F5F-442A-91F1-4CF78FA7C131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,10 +133,32 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>DurationType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffDurationType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>strength_power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>shrink_power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TurnBased</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Permanent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -676,14 +698,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -694,19 +718,24 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -717,7 +746,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -726,10 +755,15 @@
         <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -740,19 +774,24 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -762,20 +801,25 @@
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>50</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>99</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -785,64 +829,151 @@
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>25</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>99</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="1">
-        <v>0</v>
+      <c r="D6" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
         <v>99</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>30</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>99</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
